--- a/AAII_Financials/Quarterly/CRWD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRWD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>CRWD</t>
   </si>
@@ -656,467 +656,491 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44865</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44592</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43951</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43769</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43677</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43585</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43496</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43404</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43312</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43131</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1470900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1385600</v>
+      </c>
+      <c r="F8" s="3">
         <v>1305400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1234200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1169000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1103400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1058500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1010200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>963900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>921000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>845300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>786000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>731600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>692600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>637400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>580900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>535200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>487800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>431000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>380100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>337700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>302800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>264900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>232500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>199000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>178100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>152100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>125100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>108100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>96100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>80500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>66400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>55700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>47300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>342300</v>
+      </c>
+      <c r="F9" s="3">
         <v>311900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>307800</v>
       </c>
-      <c r="F9" s="3">
-        <v>303400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>289100</v>
-      </c>
       <c r="H9" s="3">
+        <v>301600</v>
+      </c>
+      <c r="I9" s="3">
+        <v>287900</v>
+      </c>
+      <c r="J9" s="3">
         <v>272700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>255100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>237400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>225000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>208600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>195000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>182900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>169200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>175600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>158200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>140600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>126800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>112600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>101700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>90400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>78500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>66700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>61500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>54400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>46900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>43400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>37400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>31600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>29300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>27000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>22300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>18600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>19400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1096900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1043400</v>
+      </c>
+      <c r="F10" s="3">
         <v>993500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>926500</v>
       </c>
-      <c r="F10" s="3">
-        <v>865600</v>
-      </c>
-      <c r="G10" s="3">
-        <v>814300</v>
-      </c>
       <c r="H10" s="3">
+        <v>867300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>815600</v>
+      </c>
+      <c r="J10" s="3">
         <v>785900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>755100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>726500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>696000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>636800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>591000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>548700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>523400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>461800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>422700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>394600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>361000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>318400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>278400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>247300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>224300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>198200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>171000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>144600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>131200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>108700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>87700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>76500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>66800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>53500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>44100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>37100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>27900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,112 +1177,120 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>444200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>408300</v>
+      </c>
+      <c r="F12" s="3">
         <v>356600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>347500</v>
       </c>
-      <c r="F12" s="3">
-        <v>330000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>334100</v>
-      </c>
       <c r="H12" s="3">
+        <v>325800</v>
+      </c>
+      <c r="I12" s="3">
+        <v>330900</v>
+      </c>
+      <c r="J12" s="3">
         <v>313800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>275600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>250900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>235200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>214000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>196100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>179400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>179100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>191800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>155300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>137900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>123400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>105000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>97600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>90500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>78200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>66100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>57500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>50500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>40600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>38700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>36000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>31600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>23900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>22000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>26000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>19000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>17600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,44 +1393,50 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-36400</v>
+      </c>
+      <c r="F14" s="3">
         <v>-3300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>38400</v>
       </c>
-      <c r="G14" s="3">
-        <v>8200</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J14" s="3">
         <v>900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M14" s="3">
         <v>-6900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-2500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1414,30 +1452,30 @@
       <c r="S14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>1000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>3100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>4300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>1600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>2100</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1447,11 +1485,11 @@
       <c r="AD14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1465,53 +1503,59 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>68800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>64400</v>
+      </c>
+      <c r="F15" s="3">
         <v>55600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>51200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>48400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>46600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>44000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>40400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>38800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>35900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>30500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>28900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>25500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>23100</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>11</v>
       </c>
@@ -1521,27 +1565,27 @@
       <c r="T15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="W15" s="3">
         <v>600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>100</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>0</v>
-      </c>
       <c r="AB15" s="3">
         <v>0</v>
       </c>
@@ -1551,11 +1595,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AF15" s="3" t="s">
-        <v>11</v>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>11</v>
@@ -1569,8 +1613,14 @@
       <c r="AJ15" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL15" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1654,230 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1504100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1416200</v>
+      </c>
+      <c r="F17" s="3">
         <v>1292300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1303200</v>
       </c>
-      <c r="F17" s="3">
-        <v>1243500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1221500</v>
-      </c>
       <c r="H17" s="3">
+        <v>1236000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1222100</v>
+      </c>
+      <c r="J17" s="3">
         <v>1139800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1065900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>950200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>914100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>815700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>782900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>747000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>712000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>698900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>637300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>583500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>511700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>454500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>420300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>385100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>334200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>280700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>256600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>229000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>200700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>183200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>163600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>158700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>121900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>111700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>108500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>86100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>80400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="F18" s="3">
         <v>13100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-69000</v>
       </c>
-      <c r="F18" s="3">
-        <v>-74600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-118100</v>
-      </c>
       <c r="H18" s="3">
+        <v>-67100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-118700</v>
+      </c>
+      <c r="J18" s="3">
         <v>-81300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-55700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>13700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>6900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>29700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>3200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-15400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-19500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-61500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-56400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-48300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-23900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-23500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-40200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-47400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-31400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-15800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-24100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-30000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-22600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-31100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-38500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-50600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-25800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-31200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-42100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-30400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-33100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-36800</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,245 +1914,259 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-2200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>2700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>2300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>24200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>17000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>11100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>3200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>1700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>4800</v>
-      </c>
-      <c r="X20" s="3">
-        <v>700</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>200</v>
       </c>
       <c r="Z20" s="3">
         <v>700</v>
       </c>
       <c r="AA20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC20" s="3">
         <v>4500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>3200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>3600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>32700</v>
+      </c>
+      <c r="F21" s="3">
         <v>69900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-15500</v>
       </c>
-      <c r="F21" s="3">
-        <v>-28900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-73800</v>
-      </c>
       <c r="H21" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-74500</v>
+      </c>
+      <c r="J21" s="3">
         <v>-37400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-15700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>51400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>43600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>61300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>31600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>8400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>3900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-15800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-15300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-1400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-21700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-30700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-12200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-20800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-29000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-45600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-20400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-26100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-38000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>-28600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>-30200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>-34300</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F22" s="3">
         <v>7600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>6900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>6800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>6700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>6700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>6600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>6500</v>
-      </c>
-      <c r="K22" s="3">
-        <v>6500</v>
-      </c>
-      <c r="L22" s="3">
-        <v>6400</v>
       </c>
       <c r="M22" s="3">
         <v>6500</v>
@@ -2097,16 +2175,16 @@
         <v>6400</v>
       </c>
       <c r="O22" s="3">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="P22" s="3">
         <v>6400</v>
       </c>
       <c r="Q22" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="R22" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="S22" s="3">
         <v>6300</v>
@@ -2115,263 +2193,281 @@
         <v>6300</v>
       </c>
       <c r="U22" s="3">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="V22" s="3">
         <v>6300</v>
       </c>
       <c r="W22" s="3">
+        <v>6400</v>
+      </c>
+      <c r="X22" s="3">
+        <v>6300</v>
+      </c>
+      <c r="Y22" s="3">
         <v>6200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>1000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>200</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>100</v>
       </c>
       <c r="AC22" s="3">
         <v>100</v>
       </c>
       <c r="AD22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF22" s="3">
         <v>200</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
       <c r="AG22" s="3">
         <v>0</v>
       </c>
       <c r="AH22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AJ22" s="3">
         <v>200</v>
       </c>
+      <c r="AK22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL22" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>39100</v>
+      </c>
+      <c r="F23" s="3">
         <v>57800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-23300</v>
       </c>
-      <c r="F23" s="3">
-        <v>-71700</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-89900</v>
-      </c>
       <c r="H23" s="3">
+        <v>-64200</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="J23" s="3">
         <v>-42400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-10500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>57600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>53900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>68600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>36300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>13100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>4900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-43600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-45800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-43500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-27000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-28200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-46000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-53100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-32800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-16200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-24100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-29400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-18200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-28100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-35100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-51300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-25400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-30900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-41800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-32500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-33500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-37000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="F24" s="3">
         <v>-3600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>10700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>6000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>21100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>46300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>6300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>10900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>7700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>13600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>9600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>4600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>4400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>5300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>8900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>4800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>3400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>13600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>4500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>4200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>50100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>2800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>1000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2570,234 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>46000</v>
+      </c>
+      <c r="F26" s="3">
         <v>61500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-34000</v>
       </c>
-      <c r="F26" s="3">
-        <v>-77600</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-111000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-70100</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-105100</v>
+      </c>
+      <c r="J26" s="3">
         <v>-88700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-16800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>46700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>46300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>54900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>26700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>8500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-48900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-54600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-48300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-30400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-41700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-50500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-57300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-82900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-24500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-29900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-19200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-28400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-35500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-51900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-31300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-42300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-32900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-33600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-37500</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>27800</v>
+      </c>
+      <c r="F27" s="3">
         <v>59400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-34000</v>
       </c>
-      <c r="F27" s="3">
-        <v>-77700</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-110200</v>
-      </c>
       <c r="H27" s="3">
+        <v>-70200</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-104300</v>
+      </c>
+      <c r="J27" s="3">
         <v>-88300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-16800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>47000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>42800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>53700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>26700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>8500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-47500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-55000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-49300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-31500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-42000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-50500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-57300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-85000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-24500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-29900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-19200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-28400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-35500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-51900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-31300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-42300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-32900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-33600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2900,14 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +3010,14 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3120,14 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3230,234 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F32" s="3">
         <v>1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>2200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-2700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-2300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-17000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-11100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-3200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-1700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-200</v>
       </c>
       <c r="Z32" s="3">
         <v>-700</v>
       </c>
       <c r="AA32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>1900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>27800</v>
+      </c>
+      <c r="F33" s="3">
         <v>59400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-34000</v>
       </c>
-      <c r="F33" s="3">
-        <v>-77700</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-110200</v>
-      </c>
       <c r="H33" s="3">
+        <v>-70200</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-104300</v>
+      </c>
+      <c r="J33" s="3">
         <v>-88300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-16800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>47000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>42800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>53700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>26700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>8500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-47500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-55000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-49300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-31500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-42000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-50500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-57300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-85000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-24500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-29900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-19200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-28400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-35500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-51900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-31300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-42300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-32900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-33600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3560,239 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>27800</v>
+      </c>
+      <c r="F35" s="3">
         <v>59400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-34000</v>
       </c>
-      <c r="F35" s="3">
-        <v>-77700</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-110200</v>
-      </c>
       <c r="H35" s="3">
+        <v>-70200</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-104300</v>
+      </c>
+      <c r="J35" s="3">
         <v>-88300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-16800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>47000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>42800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>53700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>26700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>8500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-47500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-55000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-49300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-31500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-42000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-50500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-57300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-85000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-24500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-29900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-19200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-28400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-35500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-51900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-31300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-42300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-32900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-33600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44865</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44592</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43951</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43769</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43677</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43585</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43496</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43404</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43312</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43131</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3829,10 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3869,120 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5013800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4552800</v>
+      </c>
+      <c r="F41" s="3">
         <v>5230100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4801100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4972400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4614200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4323300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4260300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4038500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3702400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3375100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2968900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3167200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2829700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2455400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2466600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2318900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2152700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1996600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1907500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1787100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1685000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1918600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1059900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1064700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1005000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>264800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>743600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>732800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>93000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>88400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>83500</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI41" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL41" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3833,26 +4011,26 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>99600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>197500</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>100000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>250000</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>11</v>
       </c>
@@ -3865,11 +4043,11 @@
       <c r="V42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3881,138 +4059,150 @@
         <v>0</v>
       </c>
       <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
         <v>647300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>90100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>94000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>82100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>103200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>108000</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI42" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ42" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL42" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1038600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>933900</v>
+      </c>
+      <c r="F43" s="3">
         <v>1429300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1013100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>886600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>808700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1135700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>813900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>661000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>702900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>853100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>561900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>539500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>461100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>626200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>485300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>418800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>369100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>368100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>283300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>266500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>211200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>239200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>172800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>149200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>144200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>165000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>145700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>115300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>87400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>92500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>77100</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI43" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ43" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL43" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4052,11 +4242,11 @@
       <c r="O44" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4115,308 +4305,326 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>389100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>353900</v>
+      </c>
+      <c r="F45" s="3">
         <v>508200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>398700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>372500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>351800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>405700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>294200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>251200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>244700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>282100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>209200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>197100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>186900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>308700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>251700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>238300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>211200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>206200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>169300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>198400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>141800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>134500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>108100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>102000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>99300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>94600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>73800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>63400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>48800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>47300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>37100</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI45" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ45" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL45" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6955200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6301600</v>
+      </c>
+      <c r="F46" s="3">
         <v>7419100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>6519300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>6534400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>6070800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6113300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5572300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>5181600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4841600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4757300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4079100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4050400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3708800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3640300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3203600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2976000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2733100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2571000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2360100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2252000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2038000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>2292300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1340800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1316000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1248500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1171600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1053200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1005400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>311300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>331400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>305600</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI46" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ46" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL46" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>69300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>66300</v>
+      </c>
+      <c r="F47" s="3">
         <v>76800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>81300</v>
-      </c>
-      <c r="F47" s="3">
-        <v>72500</v>
-      </c>
-      <c r="G47" s="3">
-        <v>71300</v>
       </c>
       <c r="H47" s="3">
         <v>72500</v>
       </c>
       <c r="I47" s="3">
+        <v>71300</v>
+      </c>
+      <c r="J47" s="3">
+        <v>72500</v>
+      </c>
+      <c r="K47" s="3">
         <v>68200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>58200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>58400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>56200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>59500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>59500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>57900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>47300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>46400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>35600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>28700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>23600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>22700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>14200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>8200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>2500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>2500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>2000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>1000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>1000</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD47" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE47" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AF47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG47" s="3">
-        <v>0</v>
+      <c r="AG47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AH47" s="3" t="s">
         <v>11</v>
@@ -4424,219 +4632,237 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AJ47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1027100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>953700</v>
+      </c>
+      <c r="F48" s="3">
         <v>861500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>817900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>765100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>709300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>687400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>657100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>571600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>564400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>561500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>461700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>517000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>498700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>532300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>455700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>411500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>345000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>292300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>276100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>250700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>228000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>203500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>200700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>193800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>174800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>136100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>129500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>108000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>86300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>73700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>59800</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI48" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ48" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL48" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2740800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2735800</v>
+      </c>
+      <c r="F49" s="3">
         <v>1684700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1673700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1198700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1194800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1189900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>967200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>960500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>955600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>859500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>917400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>600600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>589500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>517500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>519800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>505900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>510200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>513800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>456800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>459900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>463400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>99200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>99500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>8500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>8100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>8200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>8400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>8500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>8700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>9000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>9100</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI49" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ49" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL49" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4965,14 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +5075,124 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>427100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>469500</v>
+      </c>
+      <c r="F52" s="3">
         <v>194800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>316900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>201100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>178200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>99600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>96400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>89000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>92000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>76100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>39400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>31400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>28700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>289200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>244000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>225300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>218900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>217700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>184000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>159300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>143600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>135000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>106000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>96700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>87000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>87900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>64900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>49600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>51100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>19100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>15100</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI52" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ52" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL52" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5295,124 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12025000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>11270100</v>
+      </c>
+      <c r="F54" s="3">
         <v>11086700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>9965300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>9288900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>8720400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>8701600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>7783000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>7202500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>6842000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>6646500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>5831100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>5520500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5137900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5026500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>4469400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>4154200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>3835800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3618400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>3299600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>3136000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2881200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2732500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1749500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1617000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1519400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1404900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1256100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1171600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>457400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>433200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>389600</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI54" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL54" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5449,10 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,157 +5489,165 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>114500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>54200</v>
+      </c>
+      <c r="F57" s="3">
         <v>105300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>131600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>120600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>16400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>130900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>79200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>21100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>21300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>28200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>57000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>37100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>16900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>45400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>89300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>53800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>11000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>47600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>7200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>19600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>3500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>12100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>7500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>10100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>6500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>1300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>5200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>1100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>9900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>6900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>5700</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI57" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ57" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL57" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>19900</v>
+      </c>
+      <c r="F58" s="3">
         <v>18200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>15900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>12900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>12000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>13800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>15700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>17000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>16000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>14200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>14400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>16100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>16200</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -5439,288 +5705,306 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3668100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3490600</v>
+      </c>
+      <c r="F59" s="3">
         <v>3505400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2928500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2883100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2822800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2826900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2426200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2390300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2333300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2294400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1969000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1921000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1812600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2063700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1727800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1595400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1486100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1359200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1234400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1117200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>979300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>851500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>694500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>593200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>549100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>491800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>410400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>340700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>292800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>274600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>218000</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI59" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ59" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL59" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4429700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4115900</v>
+      </c>
+      <c r="F60" s="3">
         <v>4184200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3599900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3475900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3282500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3461100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3000400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2728300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2683700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2697300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2350400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2229500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2080100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2109100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1817100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1649300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1497100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1406800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1241500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1136800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>982800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>863600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>702000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>603300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>555600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>493100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>415600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>341800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>302700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>281400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>223700</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI60" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ60" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL60" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>798100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>801400</v>
+      </c>
+      <c r="F61" s="3">
         <v>801800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>802100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>797700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>773400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>775100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>776300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>774900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>777000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>778700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>780500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>774400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>778200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>741000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>740600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>740300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>739900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>739500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>739100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>738800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>738400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>738000</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5751,112 +6035,124 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>312600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>325500</v>
+      </c>
+      <c r="F62" s="3">
         <v>295700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>292600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>166900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>149100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>150800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>77400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>63900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>52500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>50100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>38900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>32800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>29800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>689000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>574100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>521400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>481800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>434400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>359400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>349000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>306600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>259100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>232700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>221600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>210600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>169200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>123400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>101700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>81900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>81700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>69300</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI62" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ62" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL62" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6255,14 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6365,14 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6475,124 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6885500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6594800</v>
+      </c>
+      <c r="F66" s="3">
         <v>6614100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5906300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5494200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5229300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5382700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4687300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4311900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4273200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4309400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3770200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3650400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3503500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3562900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>3155200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>2928800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>2733300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>2592600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2351400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>2231800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2031900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1862000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>936000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>826000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>767200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>662800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>539000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>443500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>384600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>363100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>293000</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI66" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL66" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6629,10 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6735,14 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6845,14 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6604,25 +6938,31 @@
         <v>0</v>
       </c>
       <c r="AE70" s="3">
-        <v>557900</v>
+        <v>0</v>
       </c>
       <c r="AF70" s="3">
-        <v>557900</v>
+        <v>0</v>
       </c>
       <c r="AG70" s="3">
         <v>557900</v>
       </c>
       <c r="AH70" s="3">
-        <v>0</v>
+        <v>557900</v>
       </c>
       <c r="AI70" s="3">
-        <v>0</v>
+        <v>557900</v>
       </c>
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +7065,124 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1250000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1255300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1283000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1300000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-1266000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1188300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1120500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-985800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-969000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1016000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1058800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-1112500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1139200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-1147700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-1148200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-1100700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-1045700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-996400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-964900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-922900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-872500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-815200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-730100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-711100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-686600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-656700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-637500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-609100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-573600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-521700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-519100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-487900</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI72" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL72" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7285,14 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7395,14 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7505,124 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5101700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4633900</v>
+      </c>
+      <c r="F76" s="3">
         <v>4428400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4016500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3756700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3450900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3279500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3057900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2852900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2535500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2304000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2029000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1838200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1605300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1463600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1314300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1225400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1102500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1025800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>948200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>904300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>849300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>870600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>813500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>791000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>752200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>742100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>717000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>728100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>-485200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-487800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>-461400</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI76" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL76" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7725,239 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44865</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44592</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43951</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43769</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43677</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43585</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43496</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43404</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43312</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43131</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>27800</v>
+      </c>
+      <c r="F81" s="3">
         <v>59400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-34000</v>
       </c>
-      <c r="F81" s="3">
-        <v>-77700</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-110200</v>
-      </c>
       <c r="H81" s="3">
+        <v>-70200</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-104300</v>
+      </c>
+      <c r="J81" s="3">
         <v>-88300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-16800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>47000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>42800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>53700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>26700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>8500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-47500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-55000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-49300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-31500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-42000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-50500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-57300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-85000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-24500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-29900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-19200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-28400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-35500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-51900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-31300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-42300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-32900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-33600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7994,120 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>38900</v>
+      </c>
+      <c r="F83" s="3">
         <v>36700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>34100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>32400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>29900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>25000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>24300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>21400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>18900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>16900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>13900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>12900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>12000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>27900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>23600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>21900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>20400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>20500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>17900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>16100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>14400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>11800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>10500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>9500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>8300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>7100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>5900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>5500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>5000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>4800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>3800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>3600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8210,14 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8320,14 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8430,14 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8540,14 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8650,124 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>530300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>590900</v>
+      </c>
+      <c r="F89" s="3">
         <v>497900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>397500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>332800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>384100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>345700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>326100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>326600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>383200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>347000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>273500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>244800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>300900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>273300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>242900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>209900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>215000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>159700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>159100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>108500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>147500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>114500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>88500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>55000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>98600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>66100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>38600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-6200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>1400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>15800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-28700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-6400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8804,120 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-124400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-97600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-102500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-83400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-30500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-85800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-87200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-78700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-39300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-49700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-52600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-21300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-40400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-62300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-65400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-68800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-74100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-58100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-32400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-36200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-34800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-25800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-20600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-13400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-29700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-21600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-15500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-14200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-7600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-5400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +9020,14 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +9130,124 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-151600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-994100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-123000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-490900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-48800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-101800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-325000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-105600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-54900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-51100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>20400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-468800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>41800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>66000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-319100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-97400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-79100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-61000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-93700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-44700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-41200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-384900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-17300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-98400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-23600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>634700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-572100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-34400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>4100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-10700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-36500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-87100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9284,10 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8861,11 +9327,11 @@
       <c r="O96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8924,8 +9390,14 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9500,14 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9610,14 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9720,340 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-195900</v>
+      </c>
+      <c r="F100" s="3">
         <v>51400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>4800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>74200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>2100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>46400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>62500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>33500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>2100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>49700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>7900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>29100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>5000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>38800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>4600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>26200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>7600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>36200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>2600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>760500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>5200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>27500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>6900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>27300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>680700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>8100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>182200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-4600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-1900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>5400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-4500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>1300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>5600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-2700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-1900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-2500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>5600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-2700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-1900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-2500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-3100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-1400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-1400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>1200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>800</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>100</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>460900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-598900</v>
+      </c>
+      <c r="F102" s="3">
         <v>428600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-87900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>358300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>291000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>62500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>221800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>335100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>327700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>406200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-197800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>337600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>374600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>147700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>167700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>156100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>89100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>120500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>102100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-233600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>858700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>59700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>740200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-478800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>10800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>639800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>4600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>4900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-32100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>66100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-13800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-2900</v>
       </c>
     </row>
